--- a/reports/telegram/aegis_india_2026-09-03.xlsx
+++ b/reports/telegram/aegis_india_2026-09-03.xlsx
@@ -22663,7 +22663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -22717,6 +22717,457 @@
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Advisory Warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1389 - 1464</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+5.2%) • outperforming Nifty • sector strength 71/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>no dynamic-exit protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1881 - 1982</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+7.3%) • outperforming Nifty • sector strength 79/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>no dynamic-exit protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>322 - 338</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-7.6%) • sector strength 36/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>no dynamic-exit protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>989 - 1053</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-1.7%) • outperforming Nifty • sector strength 71/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>no dynamic-exit protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>261 - 273</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-6.2%) • sector strength 36/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>no dynamic-exit protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>394 - 418</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-3.2%) • sector strength 64/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>no dynamic-exit protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>230 - 245</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-7.8%) • sector strength 57/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>no dynamic-exit protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ACCUMULATE</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>260 - 273</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-16.2%) • sector strength 29/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>no dynamic-exit protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Metal</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ACCUMULATE</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>9</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>406 - 430</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-2.5%) • sector strength 21/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>no dynamic-exit protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TATASTEEL</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Metal</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ACCUMULATE</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>178 - 190</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-4.4%) • sector strength 21/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>no dynamic-exit protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>459 - 486</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Low-risk Transport holding (low vol) • below 200-dma (-17.1%) • sector strength 7/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION de</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>no dynamic-exit protection</t>
         </is>
       </c>
     </row>
